--- a/processed_ruby_restored_xlsx/sc216_ノノ８：天体観測.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc216_ノノ８：天体観測.ss.xlsx
@@ -484,7 +484,8 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>...I thought I'd just go to sleep there with everyone.</t>
+          <t>...I thought I'd just go to sleep there with
+everyone.</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -561,8 +562,8 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>Because there are no other lights here, the stars look
-really beautiful.</t>
+          <t>Because there are no other lights here, the stars
+look really beautiful.</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -593,8 +594,8 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>Even if I think I can do it anytime, I still feel like
-it would be a waste.</t>
+          <t>Even if I think I can do it anytime, I still feel
+like it would be a waste.</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -806,8 +807,8 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>「Yes... everyone fell asleep, so I thought it couldn't
-be helped...」</t>
+          <t>「Yes... everyone fell asleep, so I thought it
+couldn't be helped...」</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -976,7 +977,8 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan lets out a breath as if recalling something.</t>
+          <t>Nono-chan lets out a breath as if recalling
+something.</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1822,8 +1824,8 @@
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>「Janitor-sensei, do you know？ Vega and Altair……between
-those two stars the Milky Way flows」</t>
+          <t>「Janitor-sensei, do you know？ Vega and
+Altair……between those two stars the Milky Way flows」</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -2539,8 +2541,8 @@
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>「Mmm... fufu！ Actually, I... feel the same... mmchu...
-chufu」</t>
+          <t>「Mmm... fufu！ Actually, I... feel the same...
+mmchu... chufu」</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2602,8 +2604,8 @@
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>「Mmm, ah！ Janitor-sensei…… Ja—Janitor… se—sensei……haa,
-nchu」</t>
+          <t>「Mmm, ah！ Janitor-sensei…… Ja—Janitor…
+se—sensei……haa, nchu」</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2772,7 +2774,8 @@
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>「Ah, nngh！ I feel like I might not be able to stop...」</t>
+          <t>「Ah, nngh！ I feel like I might not be able to
+stop...」</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -3186,7 +3189,8 @@
       <c r="B178" s="1" t="inlineStr">
         <is>
           <t>Even though her pajama was gaped open, Nono-chan
-getting excited at the full sky of stars was adorable.</t>
+getting excited at the full sky of stars was
+adorable.</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3246,8 +3250,8 @@
       </c>
       <c r="B182" s="1" t="inlineStr">
         <is>
-          <t>「Ah... s-sorry...！ I just got caught up staring at the
-stars...！」</t>
+          <t>「Ah... s-sorry...！ I just got caught up staring at
+the stars...！」</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -3460,8 +3464,8 @@
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>I reflected on my unusually cheesy behavior and looked
-back at my own words and actions.</t>
+          <t>I reflected on my unusually cheesy behavior and
+looked back at my own words and actions.</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -3631,8 +3635,8 @@
       </c>
       <c r="B207" s="1" t="inlineStr">
         <is>
-          <t>Maybe it's because we're doing it outside？ You seem to
-already be feeling it.</t>
+          <t>Maybe it's because we're doing it outside？ You seem
+to already be feeling it.</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3801,8 +3805,8 @@
       </c>
       <c r="B218" s="1" t="inlineStr">
         <is>
-          <t>At the sight of shy Nono-chan, the penis is completely
-erect.</t>
+          <t>At the sight of shy Nono-chan, the penis is
+completely erect.</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -3817,7 +3821,8 @@
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t>And I press it against Nono-chan's between (her) legs.</t>
+          <t>And I press it against Nono-chan's between (her)
+legs.</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3878,7 +3883,8 @@
       </c>
       <c r="B223" s="1" t="inlineStr">
         <is>
-          <t>「Heh heh heh, I wonder what it is that's hitting you？」</t>
+          <t>「Heh heh heh, I wonder what it is that's hitting
+you？」</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3939,8 +3945,8 @@
       </c>
       <c r="B227" s="1" t="inlineStr">
         <is>
-          <t>「I was thinking about Nono-chan... and I just couldn't
-hold back anymore...」</t>
+          <t>「I was thinking about Nono-chan... and I just
+couldn't hold back anymore...」</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -4229,8 +4235,8 @@
       </c>
       <c r="B246" s="1" t="inlineStr">
         <is>
-          <t>Embarrassed and digging her own grave, Nono-chan still
-nodded in the end.</t>
+          <t>Embarrassed and digging her own grave, Nono-chan
+still nodded in the end.</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -4275,8 +4281,8 @@
       </c>
       <c r="B249" s="1" t="inlineStr">
         <is>
-          <t>I, who could no longer hold back, said as I pressed my
-penis against her pussy.</t>
+          <t>I, who could no longer hold back, said as I pressed
+my penis against her pussy.</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -4844,8 +4850,8 @@
       </c>
       <c r="B286" s="1" t="inlineStr">
         <is>
-          <t>From the sensation of insertion, maybe she's getting a
-little used to it？</t>
+          <t>From the sensation of insertion, maybe she's getting
+a little used to it？</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -5803,8 +5809,8 @@
       </c>
       <c r="B348" s="1" t="inlineStr">
         <is>
-          <t>「Because it's true... I'll say it as many times as you
-want... Nono-chan, you're beautiful...！」</t>
+          <t>「Because it's true... I'll say it as many times as
+you want... Nono-chan, you're beautiful...！」</t>
         </is>
       </c>
       <c r="C348" t="n">
@@ -5990,8 +5996,8 @@
       <c r="B360" s="1" t="inlineStr">
         <is>
           <t>Unable to hold back my arousal, I moved my hips
-violently and my chest followed, getting stimulated in
-time.</t>
+violently and my chest followed, getting stimulated
+in time.</t>
         </is>
       </c>
       <c r="C360" t="n">
@@ -6143,8 +6149,8 @@
       </c>
       <c r="B370" s="1" t="inlineStr">
         <is>
-          <t>「Nipples... nn！ Naaah！ Ugh, they'll get even harder...
-faa, nnhah！」</t>
+          <t>「Nipples... nn！ Naaah！ Ugh, they'll get even
+harder... faa, nnhah！」</t>
         </is>
       </c>
       <c r="C370" t="n">
@@ -6299,8 +6305,8 @@
       </c>
       <c r="B380" s="1" t="inlineStr">
         <is>
-          <t>The high voice seems to pierce to the back of her head
-and race up as if climbing above the clouds.</t>
+          <t>The high voice seems to pierce to the back of her
+head and race up as if climbing above the clouds.</t>
         </is>
       </c>
       <c r="C380" t="n">
@@ -6483,8 +6489,8 @@
       </c>
       <c r="B392" s="1" t="inlineStr">
         <is>
-          <t>「Heh… if you say so, Nono-chan, it feels like we’ll be
-able to find one… fuu！」</t>
+          <t>「Heh… if you say so, Nono-chan, it feels like we’ll
+be able to find one… fuu！」</t>
         </is>
       </c>
       <c r="C392" t="n">
@@ -7241,8 +7247,8 @@
       </c>
       <c r="B441" s="1" t="inlineStr">
         <is>
-          <t>「Nnngaaaah！ No！ No, stop！ I'm… already… already, huh！？
-Fuwaa… fuwaaaah！」</t>
+          <t>「Nnngaaaah！ No！ No, stop！ I'm… already… already,
+huh！？ Fuwaa… fuwaaaah！」</t>
         </is>
       </c>
       <c r="C441" t="n">
@@ -7302,8 +7308,8 @@
       </c>
       <c r="B445" s="1" t="inlineStr">
         <is>
-          <t>Her vaginal muscles clenched in an instant… looks like
-she came.</t>
+          <t>Her vaginal muscles clenched in an instant… looks
+like she came.</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -7409,8 +7415,8 @@
       </c>
       <c r="B452" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan trembles around her mouth as she catches her
-breath.</t>
+          <t>Nono-chan trembles around her mouth as she catches
+her breath.</t>
         </is>
       </c>
       <c r="C452" t="n">
@@ -8205,9 +8211,9 @@
       </c>
       <c r="B504" s="1" t="inlineStr">
         <is>
-          <t>The penis's pulsing and the vagina's undulating rhythm
-lock perfectly together, driving them to an even
-greater height...！</t>
+          <t>The penis's pulsing and the vagina's undulating
+rhythm lock perfectly together, driving them to an
+even greater height...！</t>
         </is>
       </c>
       <c r="C504" t="n">
@@ -8405,7 +8411,8 @@
       </c>
       <c r="B517" s="1" t="inlineStr">
         <is>
-          <t>「Ha, haha... ah！ Yeah, I can't get enough... right...」</t>
+          <t>「Ha, haha... ah！ Yeah, I can't get enough...
+right...」</t>
         </is>
       </c>
       <c r="C517" t="n">
@@ -8511,8 +8518,8 @@
       </c>
       <c r="B524" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan's cry reaches my ears and I hurry to arch my
-back.</t>
+          <t>Nono-chan's cry reaches my ears and I hurry to arch
+my back.</t>
         </is>
       </c>
       <c r="C524" t="n">
@@ -8831,8 +8838,8 @@
       </c>
       <c r="B545" s="1" t="inlineStr">
         <is>
-          <t>While gazing at the starry sky, I asked playfully, but
-unfortunately she dodged the question.</t>
+          <t>While gazing at the starry sky, I asked playfully,
+but unfortunately she dodged the question.</t>
         </is>
       </c>
       <c r="C545" t="n">
@@ -9047,7 +9054,8 @@
       </c>
       <c r="B559" s="1" t="inlineStr">
         <is>
-          <t>I pointed my index finger at the sky and said proudly.</t>
+          <t>I pointed my index finger at the sky and said
+proudly.</t>
         </is>
       </c>
       <c r="C559" t="n">
@@ -9122,7 +9130,8 @@
       </c>
       <c r="B564" s="1" t="inlineStr">
         <is>
-          <t>「Okay then, next I'll give you a harder one, alright？」</t>
+          <t>「Okay then, next I'll give you a harder one,
+alright？」</t>
         </is>
       </c>
       <c r="C564" t="n">
@@ -9460,8 +9469,8 @@
       </c>
       <c r="B586" s="1" t="inlineStr">
         <is>
-          <t>「Ahaha, it's not that simple. Everyone was sleeping so
-soundly...！」</t>
+          <t>「Ahaha, it's not that simple. Everyone was sleeping
+so soundly...！」</t>
         </is>
       </c>
       <c r="C586" t="n">
@@ -9476,8 +9485,8 @@
       </c>
       <c r="B587" s="1" t="inlineStr">
         <is>
-          <t>While trying to cover it up I explained, and this time
-Rin-chan glared at me with narrowed eyes.</t>
+          <t>While trying to cover it up I explained, and this
+time Rin-chan glared at me with narrowed eyes.</t>
         </is>
       </c>
       <c r="C587" t="n">
@@ -9752,8 +9761,8 @@
       </c>
       <c r="B605" s="1" t="inlineStr">
         <is>
-          <t>When I called out to Nono-chan, her face lit up with a
-broad smile.</t>
+          <t>When I called out to Nono-chan, her face lit up with
+a broad smile.</t>
         </is>
       </c>
       <c r="C605" t="n">

--- a/processed_ruby_restored_xlsx/sc216_ノノ８：天体観測.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc216_ノノ８：天体観測.ss.xlsx
@@ -716,7 +716,7 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Hajime</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>Hajime</t>
+          <t>Nono</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>「Nnnu…! Fu…! Haa, haa…!」</t>
+          <t>Nnnu…! Fu…! Haa, haa…!</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -3666,8 +3666,8 @@
       </c>
       <c r="B209" s="1" t="inlineStr">
         <is>
-          <t>「Your nipple, oh, look… smooch！ It's all puffy…
-smooch…！」</t>
+          <t>Your nipple, oh, look… smooch！ It」s all puffy…
+smooch…！</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3697,8 +3697,7 @@
       </c>
       <c r="B211" s="1" t="inlineStr">
         <is>
-          <t>「Ahf, ahfuu... fuaaaa, aaah！ No... don't smooch
-me...！」</t>
+          <t>Ahf, ahfuu... fuaaaa, aaah！ No... don't smooch me...！</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -4008,8 +4007,8 @@
       </c>
       <c r="B231" s="1" t="inlineStr">
         <is>
-          <t>「Hah, haaah...！ W-wait, me too... I can't... hold
-it... anymore, but...」</t>
+          <t>Hah, haaah...！ W-wait, me too... I can't... hold
+it... anymore, but...</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -4389,7 +4388,7 @@
       </c>
       <c r="B256" s="1" t="inlineStr">
         <is>
-          <t>「Ha, fhaaa... ah, ah... n, fua, ah, aah...」</t>
+          <t>Ha, fhaaa... ah, ah... n, fua, ah, aah...</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -4680,8 +4679,8 @@
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
-          <t>「Nn fufu, huh！ Faa… nnhh！ Then we can stay connected
-forever… ufufu…！」</t>
+          <t>Nn fufu, huh！ Faa… nnhh！ Then we can stay connected
+forever… ufufu…！</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4711,7 +4710,7 @@
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
-          <t>My smile and those gentle yet lewd words arouse me,
+          <t>His smile and those gentle yet lewd words arouse me,
 and my penis swells even more inside.</t>
         </is>
       </c>
@@ -4942,8 +4941,8 @@
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t>「Nnngh, ha... ha！ Ugh... it already feels so good...
-ngh, ha！ Haaa...！」</t>
+          <t>Nnngh, ha... ha！ Ugh... it already feels so good...
+ngh, ha！ Haaa...！</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -4973,8 +4972,8 @@
       </c>
       <c r="B294" s="1" t="inlineStr">
         <is>
-          <t>「Heh heh... this might turn into something serious,
-huh？」</t>
+          <t>Heh heh... this might turn into something serious,
+huh？</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -6599,8 +6598,8 @@
       </c>
       <c r="B399" s="1" t="inlineStr">
         <is>
-          <t>「Nn！ Nn！ Nnnh！ Ahh... Se-sensei！ It's... intense！ So
-intense...！」</t>
+          <t>Nn！ Nn！ Nnnh！ Ahh... Se-sensei！ It's... intense！ So
+intense...！</t>
         </is>
       </c>
       <c r="C399" t="n">
@@ -6645,7 +6644,7 @@
       </c>
       <c r="B402" s="1" t="inlineStr">
         <is>
-          <t>I thrust my hips upward as if lifting from below.</t>
+          <t>He thrust his hips upward as if lifting from below.</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -6707,8 +6706,8 @@
       </c>
       <c r="B406" s="1" t="inlineStr">
         <is>
-          <t>「Nngh—fuuh！ More...！ Aah！ More... more... I want it！
-Haaah, nngh！」</t>
+          <t>Nngh—fuuh！ More...！ Aah！ More... more... I want it！
+Haaah, nngh！</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -6909,7 +6908,7 @@
       </c>
       <c r="B419" s="1" t="inlineStr">
         <is>
-          <t>I find the sight of her so unbearably dear that,
+          <t>I find the sight of them so unbearably dear that,
 pushing the penis deep inside, I pick up the pace and
 keep thrusting my hips.</t>
         </is>
@@ -7018,8 +7017,8 @@
       </c>
       <c r="B426" s="1" t="inlineStr">
         <is>
-          <t>「Ahh！ Yoo, mui-n, sen... nngh ah！ Teacher！ Teacher...
-nngh！ Ngh！ Ngh！ Ngh！」</t>
+          <t>Ahh！ Yoo, mui-n, sen... nngh ah！ Teacher！ Teacher...
+nngh！ Ngh！ Ngh！ Ngh！</t>
         </is>
       </c>
       <c r="C426" t="n">
@@ -7156,8 +7155,8 @@
       </c>
       <c r="B435" s="1" t="inlineStr">
         <is>
-          <t>「Nn—ah...！ Ah！ Muin, teacher...！ Ah！ I... I, I...
-already...！」</t>
+          <t>Nn—ah...！ Ah！ Muin, teacher...！ Ah！ I... I, I...
+already...！</t>
         </is>
       </c>
       <c r="C435" t="n">
@@ -7462,7 +7461,7 @@
       </c>
       <c r="B455" s="1" t="inlineStr">
         <is>
-          <t>「Ahhh...！ Ah, Muin, teacher...」</t>
+          <t>Ahhh...！ Ah, Muin, teacher...</t>
         </is>
       </c>
       <c r="C455" t="n">
@@ -7477,7 +7476,7 @@
       </c>
       <c r="B456" s="1" t="inlineStr">
         <is>
-          <t>The way she calls me with those vacant eyes is so
+          <t>The way they call me with those vacant eyes is so
 cute…！</t>
         </is>
       </c>
@@ -7585,7 +7584,7 @@
       </c>
       <c r="B463" s="1" t="inlineStr">
         <is>
-          <t>It's like she came after being creamed on......</t>
+          <t>It's like they came after being creamed on......</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -8120,8 +8119,8 @@
       </c>
       <c r="B498" s="1" t="inlineStr">
         <is>
-          <t>「Hafu, ah！ Janitor-sensei... uuuuh~！ I'm... coming
-too！ I'm gonna cum...！」</t>
+          <t>Hafu, ah！ Janitor-sensei... uuuuh~！ I'm... coming
+too！ I'm gonna cum...！</t>
         </is>
       </c>
       <c r="C498" t="n">
@@ -8916,7 +8915,7 @@
       </c>
       <c r="B550" s="1" t="inlineStr">
         <is>
-          <t>「So then, Janitor-sensei？ Do you get it this time？」</t>
+          <t>So then, Janitor-sensei？ Do you get it this time？</t>
         </is>
       </c>
       <c r="C550" t="n">
